--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N160_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N160_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.68548219516936</v>
+        <v>6.611390856715022</v>
       </c>
       <c r="D2" t="n">
-        <v>1.84940515092878</v>
+        <v>0.3005283370259267</v>
       </c>
       <c r="E2" t="n">
-        <v>14.49354338182187</v>
+        <v>2.355200799546054</v>
       </c>
       <c r="F2" t="n">
-        <v>13.73722230909503</v>
+        <v>2.232298625227942</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>35.42562062111632</v>
+        <v>5.756663350931403</v>
       </c>
       <c r="D3" t="n">
-        <v>34.99563464840215</v>
+        <v>5.686790630365349</v>
       </c>
       <c r="E3" t="n">
-        <v>14.49354338182187</v>
+        <v>2.355200799546054</v>
       </c>
       <c r="F3" t="n">
-        <v>13.73722230909503</v>
+        <v>2.232298625227942</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.73513062155478</v>
+        <v>6.781958726002652</v>
       </c>
       <c r="D4" t="n">
-        <v>27.2071510397023</v>
+        <v>4.421162043951623</v>
       </c>
       <c r="E4" t="n">
-        <v>14.49354338182187</v>
+        <v>2.355200799546054</v>
       </c>
       <c r="F4" t="n">
-        <v>13.73722230909503</v>
+        <v>2.232298625227942</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>3.806676909894772</v>
+        <v>0.6185849978579004</v>
       </c>
       <c r="D5" t="n">
-        <v>5.048407202753042</v>
+        <v>0.8203661704473694</v>
       </c>
       <c r="E5" t="n">
-        <v>14.49354338182187</v>
+        <v>2.355200799546054</v>
       </c>
       <c r="F5" t="n">
-        <v>13.73722230909503</v>
+        <v>2.232298625227942</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.14032637173394</v>
+        <v>5.060303035406766</v>
       </c>
       <c r="D6" t="n">
-        <v>27.04163456597992</v>
+        <v>4.394265616971737</v>
       </c>
       <c r="E6" t="n">
-        <v>14.49354338182187</v>
+        <v>2.355200799546054</v>
       </c>
       <c r="F6" t="n">
-        <v>13.73722230909503</v>
+        <v>2.232298625227942</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>15.66297794017731</v>
+        <v>2.545233915278814</v>
       </c>
       <c r="D7" t="n">
-        <v>17.33630274712142</v>
+        <v>2.817149196407231</v>
       </c>
       <c r="E7" t="n">
-        <v>14.49354338182187</v>
+        <v>2.355200799546054</v>
       </c>
       <c r="F7" t="n">
-        <v>13.73722230909503</v>
+        <v>2.232298625227942</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>43.65394479580371</v>
+        <v>7.093766029318103</v>
       </c>
       <c r="D8" t="n">
-        <v>36.50342449688796</v>
+        <v>5.931806480744293</v>
       </c>
       <c r="E8" t="n">
-        <v>14.49354338182187</v>
+        <v>2.355200799546054</v>
       </c>
       <c r="F8" t="n">
-        <v>13.73722230909503</v>
+        <v>2.232298625227942</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>25.88187071478278</v>
+        <v>4.205803991152202</v>
       </c>
       <c r="D9" t="n">
-        <v>28.76351963215794</v>
+        <v>4.674071940225666</v>
       </c>
       <c r="E9" t="n">
-        <v>14.49354338182187</v>
+        <v>2.355200799546054</v>
       </c>
       <c r="F9" t="n">
-        <v>13.73722230909503</v>
+        <v>2.232298625227942</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>47.75470674697349</v>
+        <v>7.760139846383193</v>
       </c>
       <c r="D10" t="n">
-        <v>46.86229835423002</v>
+        <v>7.615123482562378</v>
       </c>
       <c r="E10" t="n">
-        <v>14.49354338182187</v>
+        <v>2.355200799546054</v>
       </c>
       <c r="F10" t="n">
-        <v>13.73722230909503</v>
+        <v>2.232298625227942</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>5.132561647465486</v>
+        <v>0.8340412677131416</v>
       </c>
       <c r="D11" t="n">
-        <v>7.166572373136625</v>
+        <v>1.164568010634702</v>
       </c>
       <c r="E11" t="n">
-        <v>14.49354338182187</v>
+        <v>2.355200799546054</v>
       </c>
       <c r="F11" t="n">
-        <v>13.73722230909503</v>
+        <v>2.232298625227942</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>32.00398019510468</v>
+        <v>5.200646781704511</v>
       </c>
       <c r="D12" t="n">
-        <v>31.48977627511796</v>
+        <v>5.117088644706669</v>
       </c>
       <c r="E12" t="n">
-        <v>14.49354338182187</v>
+        <v>2.355200799546054</v>
       </c>
       <c r="F12" t="n">
-        <v>13.73722230909503</v>
+        <v>2.232298625227942</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
